--- a/src/width_txt/Разрядность_элементов_фильтра_Гилберта_задержки_АЦП_№2.xlsx
+++ b/src/width_txt/Разрядность_элементов_фильтра_Гилберта_задержки_АЦП_№2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="608" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="912" uniqueCount="76">
   <si>
     <t>Row</t>
   </si>
@@ -357,7 +357,7 @@
         <v>30</v>
       </c>
       <c r="C6" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -368,7 +368,7 @@
         <v>35</v>
       </c>
       <c r="C7" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -379,7 +379,7 @@
         <v>30</v>
       </c>
       <c r="C8" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -401,7 +401,7 @@
         <v>30</v>
       </c>
       <c r="C10" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -423,7 +423,7 @@
         <v>30</v>
       </c>
       <c r="C12" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -434,7 +434,7 @@
         <v>38</v>
       </c>
       <c r="C13" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -445,7 +445,7 @@
         <v>30</v>
       </c>
       <c r="C14" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -456,7 +456,7 @@
         <v>39</v>
       </c>
       <c r="C15" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
@@ -467,7 +467,7 @@
         <v>30</v>
       </c>
       <c r="C16" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
@@ -478,7 +478,7 @@
         <v>39</v>
       </c>
       <c r="C17" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
@@ -489,7 +489,7 @@
         <v>30</v>
       </c>
       <c r="C18" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -500,7 +500,7 @@
         <v>40</v>
       </c>
       <c r="C19" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -511,7 +511,7 @@
         <v>30</v>
       </c>
       <c r="C20" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -522,7 +522,7 @@
         <v>40</v>
       </c>
       <c r="C21" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
@@ -533,7 +533,7 @@
         <v>30</v>
       </c>
       <c r="C22" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
@@ -566,7 +566,7 @@
         <v>41</v>
       </c>
       <c r="C25" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26">
@@ -577,7 +577,7 @@
         <v>30</v>
       </c>
       <c r="C26" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
@@ -610,7 +610,7 @@
         <v>42</v>
       </c>
       <c r="C29" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
@@ -621,7 +621,7 @@
         <v>30</v>
       </c>
       <c r="C30" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31">
@@ -632,7 +632,7 @@
         <v>43</v>
       </c>
       <c r="C31" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32">
@@ -643,7 +643,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33">
@@ -654,7 +654,7 @@
         <v>43</v>
       </c>
       <c r="C33" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34">
@@ -665,7 +665,7 @@
         <v>30</v>
       </c>
       <c r="C34" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35">
@@ -676,7 +676,7 @@
         <v>44</v>
       </c>
       <c r="C35" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -687,7 +687,7 @@
         <v>30</v>
       </c>
       <c r="C36" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37">
@@ -698,7 +698,7 @@
         <v>46</v>
       </c>
       <c r="C37" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38">
@@ -709,7 +709,7 @@
         <v>30</v>
       </c>
       <c r="C38" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39">
@@ -720,7 +720,7 @@
         <v>46</v>
       </c>
       <c r="C39" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40">
@@ -731,7 +731,7 @@
         <v>30</v>
       </c>
       <c r="C40" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -742,7 +742,7 @@
         <v>44</v>
       </c>
       <c r="C41" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -753,7 +753,7 @@
         <v>30</v>
       </c>
       <c r="C42" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -764,7 +764,7 @@
         <v>43</v>
       </c>
       <c r="C43" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -775,7 +775,7 @@
         <v>30</v>
       </c>
       <c r="C44" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45">
@@ -786,7 +786,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46">
@@ -797,7 +797,7 @@
         <v>30</v>
       </c>
       <c r="C46" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
@@ -808,7 +808,7 @@
         <v>42</v>
       </c>
       <c r="C47" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48">
@@ -819,7 +819,7 @@
         <v>30</v>
       </c>
       <c r="C48" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -830,7 +830,7 @@
         <v>42</v>
       </c>
       <c r="C49" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -841,7 +841,7 @@
         <v>30</v>
       </c>
       <c r="C50" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -852,7 +852,7 @@
         <v>41</v>
       </c>
       <c r="C51" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -863,7 +863,7 @@
         <v>30</v>
       </c>
       <c r="C52" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53">
@@ -874,7 +874,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54">
@@ -885,7 +885,7 @@
         <v>30</v>
       </c>
       <c r="C54" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55">
@@ -896,7 +896,7 @@
         <v>40</v>
       </c>
       <c r="C55" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56">
@@ -907,7 +907,7 @@
         <v>30</v>
       </c>
       <c r="C56" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57">
@@ -918,7 +918,7 @@
         <v>40</v>
       </c>
       <c r="C57" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58">
@@ -929,7 +929,7 @@
         <v>30</v>
       </c>
       <c r="C58" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59">
@@ -940,7 +940,7 @@
         <v>39</v>
       </c>
       <c r="C59" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60">
@@ -951,7 +951,7 @@
         <v>30</v>
       </c>
       <c r="C60" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61">
@@ -962,7 +962,7 @@
         <v>39</v>
       </c>
       <c r="C61" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62">
@@ -973,7 +973,7 @@
         <v>30</v>
       </c>
       <c r="C62" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63">
@@ -984,7 +984,7 @@
         <v>38</v>
       </c>
       <c r="C63" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64">
@@ -995,7 +995,7 @@
         <v>30</v>
       </c>
       <c r="C64" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65">
@@ -1006,7 +1006,7 @@
         <v>37</v>
       </c>
       <c r="C65" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66">
@@ -1017,7 +1017,7 @@
         <v>30</v>
       </c>
       <c r="C66" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67">
@@ -1028,7 +1028,7 @@
         <v>36</v>
       </c>
       <c r="C67" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68">
@@ -1039,7 +1039,7 @@
         <v>30</v>
       </c>
       <c r="C68" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69">
@@ -1050,7 +1050,7 @@
         <v>35</v>
       </c>
       <c r="C69" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70">
@@ -1061,7 +1061,7 @@
         <v>30</v>
       </c>
       <c r="C70" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="71">
@@ -1072,7 +1072,7 @@
         <v>34</v>
       </c>
       <c r="C71" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72">
@@ -1083,7 +1083,7 @@
         <v>30</v>
       </c>
       <c r="C72" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="73">
@@ -1094,7 +1094,7 @@
         <v>30</v>
       </c>
       <c r="C73" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74">
